--- a/price-list-export.xlsx
+++ b/price-list-export.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\Leeukopf-Website-Official\gelitup-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Leeukopf-Website-Official\gelitup-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F77C4D-8E40-4AED-80CF-407F41874850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172CB0B9-D314-4A3E-9F5D-6DE2142CFC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="1085">
   <si>
     <t>Item Name</t>
   </si>
@@ -1738,9 +1738,6 @@
     <t>2113D Rose Moonlight -HTF</t>
   </si>
   <si>
-    <t>2113E Star Child -HTF</t>
-  </si>
-  <si>
     <t>2113F Jet Black Flash -HTF</t>
   </si>
   <si>
@@ -1762,9 +1759,6 @@
     <t>2113N Pink My Grey -HTF</t>
   </si>
   <si>
-    <t>2113O Opa -HTF</t>
-  </si>
-  <si>
     <t>2113P Flash-Berry -HTF</t>
   </si>
   <si>
@@ -2149,12 +2143,6 @@
     <t>SS03 SPIX and SPEX Giddy Grape -HTF</t>
   </si>
   <si>
-    <t>SS04 SPIX and SPEX Popping Candy -HTF</t>
-  </si>
-  <si>
-    <t>SS05 SPIX and SPEX Lemon Sorbet -HTF</t>
-  </si>
-  <si>
     <t>SS06 SPIX and SPEX Tusk Tusk -HTF</t>
   </si>
   <si>
@@ -2716,9 +2704,6 @@
     <t>MultiMix Synthogel 60gr Glitter White -HTF</t>
   </si>
   <si>
-    <t>MultiMix Syntholiquid 100ml -HTF</t>
-  </si>
-  <si>
     <t>Dazzle Me 1gr GP06-Extreme Mirror</t>
   </si>
   <si>
@@ -3239,6 +3224,57 @@
   </si>
   <si>
     <t>All In One Liquid 500 ml -HTF</t>
+  </si>
+  <si>
+    <t>Premium Builder Gel Blue 40g -HTF</t>
+  </si>
+  <si>
+    <t>Premium Builder Gel Mint 40g -HTF</t>
+  </si>
+  <si>
+    <t>Premium Builder Gel Purple 40g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Electric Orchid 20g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Warm Sand Glow 20g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Supernova Indigo 20g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Stardust Plum 20g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Rose Stardust 20g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Cosmic Dust 20g -HTF</t>
+  </si>
+  <si>
+    <t>3-in-1 Glitter - Copper Sunshine 20g -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE01 -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE02 -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE03 -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE04 -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE05 -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE06 -HTF</t>
+  </si>
+  <si>
+    <t>Neon Cat Eye #NCE07 -HTF</t>
   </si>
 </sst>
 </file>
@@ -3500,7 +3536,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C1080"/>
+  <dimension ref="A1:C1093"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.33203125" customWidth="1"/>
@@ -3696,10 +3732,10 @@
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="C18" s="1">
         <v>7.41</v>
@@ -5825,7 +5861,7 @@
         <v>211</v>
       </c>
       <c r="C211" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5836,7 +5872,7 @@
         <v>212</v>
       </c>
       <c r="C212" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5847,7 +5883,7 @@
         <v>213</v>
       </c>
       <c r="C213" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5858,7 +5894,7 @@
         <v>214</v>
       </c>
       <c r="C214" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5869,7 +5905,7 @@
         <v>215</v>
       </c>
       <c r="C215" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5880,7 +5916,7 @@
         <v>216</v>
       </c>
       <c r="C216" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5891,7 +5927,7 @@
         <v>217</v>
       </c>
       <c r="C217" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5902,7 +5938,7 @@
         <v>218</v>
       </c>
       <c r="C218" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5913,7 +5949,7 @@
         <v>219</v>
       </c>
       <c r="C219" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5924,7 +5960,7 @@
         <v>220</v>
       </c>
       <c r="C220" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5935,7 +5971,7 @@
         <v>221</v>
       </c>
       <c r="C221" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5946,7 +5982,7 @@
         <v>222</v>
       </c>
       <c r="C222" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5957,7 +5993,7 @@
         <v>223</v>
       </c>
       <c r="C223" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5968,7 +6004,7 @@
         <v>224</v>
       </c>
       <c r="C224" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5979,7 +6015,7 @@
         <v>225</v>
       </c>
       <c r="C225" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5990,7 +6026,7 @@
         <v>226</v>
       </c>
       <c r="C226" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6001,7 +6037,7 @@
         <v>227</v>
       </c>
       <c r="C227" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6012,7 +6048,7 @@
         <v>228</v>
       </c>
       <c r="C228" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6023,7 +6059,7 @@
         <v>229</v>
       </c>
       <c r="C229" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6166,7 +6202,7 @@
         <v>242</v>
       </c>
       <c r="C242" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6210,7 +6246,7 @@
         <v>246</v>
       </c>
       <c r="C246" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6221,7 +6257,7 @@
         <v>247</v>
       </c>
       <c r="C247" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6232,7 +6268,7 @@
         <v>248</v>
       </c>
       <c r="C248" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6265,7 +6301,7 @@
         <v>251</v>
       </c>
       <c r="C251" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9532,7 +9568,7 @@
         <v>548</v>
       </c>
       <c r="C548" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9543,7 +9579,7 @@
         <v>549</v>
       </c>
       <c r="C549" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9554,7 +9590,7 @@
         <v>550</v>
       </c>
       <c r="C550" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9565,7 +9601,7 @@
         <v>551</v>
       </c>
       <c r="C551" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9576,7 +9612,7 @@
         <v>552</v>
       </c>
       <c r="C552" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9587,7 +9623,7 @@
         <v>553</v>
       </c>
       <c r="C553" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9598,7 +9634,7 @@
         <v>554</v>
       </c>
       <c r="C554" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9609,7 +9645,7 @@
         <v>555</v>
       </c>
       <c r="C555" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9620,7 +9656,7 @@
         <v>556</v>
       </c>
       <c r="C556" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9631,7 +9667,7 @@
         <v>557</v>
       </c>
       <c r="C557" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9642,7 +9678,7 @@
         <v>558</v>
       </c>
       <c r="C558" s="1">
-        <v>8.27</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9653,7 +9689,7 @@
         <v>559</v>
       </c>
       <c r="C559" s="1">
-        <v>8.27</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9664,7 +9700,7 @@
         <v>560</v>
       </c>
       <c r="C560" s="1">
-        <v>8.27</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9675,7 +9711,7 @@
         <v>561</v>
       </c>
       <c r="C561" s="1">
-        <v>8.27</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9686,7 +9722,7 @@
         <v>562</v>
       </c>
       <c r="C562" s="1">
-        <v>7.68</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9697,7 +9733,7 @@
         <v>563</v>
       </c>
       <c r="C563" s="1">
-        <v>7.68</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9708,7 +9744,7 @@
         <v>564</v>
       </c>
       <c r="C564" s="1">
-        <v>7.68</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9719,7 +9755,7 @@
         <v>565</v>
       </c>
       <c r="C565" s="1">
-        <v>7.68</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9730,7 +9766,7 @@
         <v>566</v>
       </c>
       <c r="C566" s="1">
-        <v>7.68</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9741,7 +9777,7 @@
         <v>567</v>
       </c>
       <c r="C567" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9752,7 +9788,7 @@
         <v>568</v>
       </c>
       <c r="C568" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9763,7 +9799,7 @@
         <v>569</v>
       </c>
       <c r="C569" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9774,7 +9810,7 @@
         <v>570</v>
       </c>
       <c r="C570" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9785,7 +9821,7 @@
         <v>571</v>
       </c>
       <c r="C571" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9796,7 +9832,7 @@
         <v>572</v>
       </c>
       <c r="C572" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9807,7 +9843,7 @@
         <v>573</v>
       </c>
       <c r="C573" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9818,7 +9854,7 @@
         <v>574</v>
       </c>
       <c r="C574" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9829,7 +9865,7 @@
         <v>575</v>
       </c>
       <c r="C575" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9840,7 +9876,7 @@
         <v>576</v>
       </c>
       <c r="C576" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9851,7 +9887,7 @@
         <v>577</v>
       </c>
       <c r="C577" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9862,7 +9898,7 @@
         <v>578</v>
       </c>
       <c r="C578" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9873,7 +9909,7 @@
         <v>579</v>
       </c>
       <c r="C579" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9884,7 +9920,7 @@
         <v>580</v>
       </c>
       <c r="C580" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9895,7 +9931,7 @@
         <v>581</v>
       </c>
       <c r="C581" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9906,7 +9942,7 @@
         <v>582</v>
       </c>
       <c r="C582" s="1">
-        <v>7.36</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9917,7 +9953,7 @@
         <v>583</v>
       </c>
       <c r="C583" s="1">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9928,7 +9964,7 @@
         <v>584</v>
       </c>
       <c r="C584" s="1">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9950,7 +9986,7 @@
         <v>586</v>
       </c>
       <c r="C586" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9961,7 +9997,7 @@
         <v>587</v>
       </c>
       <c r="C587" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9972,7 +10008,7 @@
         <v>588</v>
       </c>
       <c r="C588" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9983,7 +10019,7 @@
         <v>589</v>
       </c>
       <c r="C589" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9994,7 +10030,7 @@
         <v>590</v>
       </c>
       <c r="C590" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10005,7 +10041,7 @@
         <v>591</v>
       </c>
       <c r="C591" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10016,7 +10052,7 @@
         <v>592</v>
       </c>
       <c r="C592" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10027,7 +10063,7 @@
         <v>593</v>
       </c>
       <c r="C593" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10038,7 +10074,7 @@
         <v>594</v>
       </c>
       <c r="C594" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10049,7 +10085,7 @@
         <v>595</v>
       </c>
       <c r="C595" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10060,7 +10096,7 @@
         <v>596</v>
       </c>
       <c r="C596" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10071,7 +10107,7 @@
         <v>597</v>
       </c>
       <c r="C597" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10082,7 +10118,7 @@
         <v>598</v>
       </c>
       <c r="C598" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10093,7 +10129,7 @@
         <v>599</v>
       </c>
       <c r="C599" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10104,7 +10140,7 @@
         <v>600</v>
       </c>
       <c r="C600" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="601" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10115,7 +10151,7 @@
         <v>601</v>
       </c>
       <c r="C601" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10126,7 +10162,7 @@
         <v>602</v>
       </c>
       <c r="C602" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10137,7 +10173,7 @@
         <v>603</v>
       </c>
       <c r="C603" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="604" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10148,7 +10184,7 @@
         <v>604</v>
       </c>
       <c r="C604" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="605" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10159,7 +10195,7 @@
         <v>605</v>
       </c>
       <c r="C605" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10170,7 +10206,7 @@
         <v>606</v>
       </c>
       <c r="C606" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="607" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10181,7 +10217,7 @@
         <v>607</v>
       </c>
       <c r="C607" s="1">
-        <v>8.32</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="608" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10192,7 +10228,7 @@
         <v>608</v>
       </c>
       <c r="C608" s="1">
-        <v>8.32</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="609" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10214,7 +10250,7 @@
         <v>610</v>
       </c>
       <c r="C610" s="1">
-        <v>7.41</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10225,7 +10261,7 @@
         <v>611</v>
       </c>
       <c r="C611" s="1">
-        <v>7.41</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="612" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10236,7 +10272,7 @@
         <v>612</v>
       </c>
       <c r="C612" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="613" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10247,7 +10283,7 @@
         <v>613</v>
       </c>
       <c r="C613" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10258,7 +10294,7 @@
         <v>614</v>
       </c>
       <c r="C614" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="615" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10269,7 +10305,7 @@
         <v>615</v>
       </c>
       <c r="C615" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="616" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10280,7 +10316,7 @@
         <v>616</v>
       </c>
       <c r="C616" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="617" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10291,7 +10327,7 @@
         <v>617</v>
       </c>
       <c r="C617" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="618" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10302,7 +10338,7 @@
         <v>618</v>
       </c>
       <c r="C618" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="619" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10313,7 +10349,7 @@
         <v>619</v>
       </c>
       <c r="C619" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="620" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10324,7 +10360,7 @@
         <v>620</v>
       </c>
       <c r="C620" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="621" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10335,7 +10371,7 @@
         <v>621</v>
       </c>
       <c r="C621" s="1">
-        <v>9.0299999999999994</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="622" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10346,7 +10382,7 @@
         <v>622</v>
       </c>
       <c r="C622" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10357,7 +10393,7 @@
         <v>623</v>
       </c>
       <c r="C623" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="624" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10368,7 +10404,7 @@
         <v>624</v>
       </c>
       <c r="C624" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="625" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10379,7 +10415,7 @@
         <v>625</v>
       </c>
       <c r="C625" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10390,7 +10426,7 @@
         <v>626</v>
       </c>
       <c r="C626" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="627" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10401,7 +10437,7 @@
         <v>627</v>
       </c>
       <c r="C627" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10412,7 +10448,7 @@
         <v>628</v>
       </c>
       <c r="C628" s="1">
-        <v>8.32</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="629" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10423,7 +10459,7 @@
         <v>629</v>
       </c>
       <c r="C629" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10434,7 +10470,7 @@
         <v>630</v>
       </c>
       <c r="C630" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10445,7 +10481,7 @@
         <v>631</v>
       </c>
       <c r="C631" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10456,7 +10492,7 @@
         <v>632</v>
       </c>
       <c r="C632" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="633" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10467,7 +10503,7 @@
         <v>633</v>
       </c>
       <c r="C633" s="1">
-        <v>9.67</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="634" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10478,7 +10514,7 @@
         <v>634</v>
       </c>
       <c r="C634" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10489,7 +10525,7 @@
         <v>635</v>
       </c>
       <c r="C635" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10500,7 +10536,7 @@
         <v>636</v>
       </c>
       <c r="C636" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10511,7 +10547,7 @@
         <v>637</v>
       </c>
       <c r="C637" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10522,7 +10558,7 @@
         <v>638</v>
       </c>
       <c r="C638" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="639" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10533,7 +10569,7 @@
         <v>639</v>
       </c>
       <c r="C639" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="640" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10544,7 +10580,7 @@
         <v>640</v>
       </c>
       <c r="C640" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10555,7 +10591,7 @@
         <v>641</v>
       </c>
       <c r="C641" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10566,7 +10602,7 @@
         <v>642</v>
       </c>
       <c r="C642" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10577,7 +10613,7 @@
         <v>643</v>
       </c>
       <c r="C643" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10588,7 +10624,7 @@
         <v>644</v>
       </c>
       <c r="C644" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="645" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10599,7 +10635,7 @@
         <v>645</v>
       </c>
       <c r="C645" s="1">
-        <v>9.67</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="646" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10610,7 +10646,7 @@
         <v>646</v>
       </c>
       <c r="C646" s="1">
-        <v>9.67</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="647" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10621,7 +10657,7 @@
         <v>647</v>
       </c>
       <c r="C647" s="1">
-        <v>9.67</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="648" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10632,7 +10668,7 @@
         <v>648</v>
       </c>
       <c r="C648" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="649" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10643,7 +10679,7 @@
         <v>649</v>
       </c>
       <c r="C649" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="650" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10654,7 +10690,7 @@
         <v>650</v>
       </c>
       <c r="C650" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="651" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10665,7 +10701,7 @@
         <v>651</v>
       </c>
       <c r="C651" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10676,7 +10712,7 @@
         <v>652</v>
       </c>
       <c r="C652" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="653" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10687,7 +10723,7 @@
         <v>653</v>
       </c>
       <c r="C653" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="654" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10698,7 +10734,7 @@
         <v>654</v>
       </c>
       <c r="C654" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="655" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10709,7 +10745,7 @@
         <v>655</v>
       </c>
       <c r="C655" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10720,7 +10756,7 @@
         <v>656</v>
       </c>
       <c r="C656" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10731,7 +10767,7 @@
         <v>657</v>
       </c>
       <c r="C657" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10742,7 +10778,7 @@
         <v>658</v>
       </c>
       <c r="C658" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10753,7 +10789,7 @@
         <v>659</v>
       </c>
       <c r="C659" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10764,7 +10800,7 @@
         <v>660</v>
       </c>
       <c r="C660" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="661" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10775,7 +10811,7 @@
         <v>661</v>
       </c>
       <c r="C661" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="662" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10786,7 +10822,7 @@
         <v>662</v>
       </c>
       <c r="C662" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="663" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10797,7 +10833,7 @@
         <v>663</v>
       </c>
       <c r="C663" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="664" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10808,7 +10844,7 @@
         <v>664</v>
       </c>
       <c r="C664" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="665" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10819,7 +10855,7 @@
         <v>665</v>
       </c>
       <c r="C665" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="666" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10830,7 +10866,7 @@
         <v>666</v>
       </c>
       <c r="C666" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="667" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10841,7 +10877,7 @@
         <v>667</v>
       </c>
       <c r="C667" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="668" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10852,7 +10888,7 @@
         <v>668</v>
       </c>
       <c r="C668" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="669" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10863,7 +10899,7 @@
         <v>669</v>
       </c>
       <c r="C669" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="670" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10874,7 +10910,7 @@
         <v>670</v>
       </c>
       <c r="C670" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="671" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10885,7 +10921,7 @@
         <v>671</v>
       </c>
       <c r="C671" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="672" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10896,7 +10932,7 @@
         <v>672</v>
       </c>
       <c r="C672" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="673" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10907,7 +10943,7 @@
         <v>673</v>
       </c>
       <c r="C673" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="674" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10918,7 +10954,7 @@
         <v>674</v>
       </c>
       <c r="C674" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="675" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10929,7 +10965,7 @@
         <v>675</v>
       </c>
       <c r="C675" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="676" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10940,7 +10976,7 @@
         <v>676</v>
       </c>
       <c r="C676" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="677" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10951,7 +10987,7 @@
         <v>677</v>
       </c>
       <c r="C677" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="678" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10962,7 +10998,7 @@
         <v>678</v>
       </c>
       <c r="C678" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="679" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10973,7 +11009,7 @@
         <v>679</v>
       </c>
       <c r="C679" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="680" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10984,7 +11020,7 @@
         <v>680</v>
       </c>
       <c r="C680" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="681" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10995,7 +11031,7 @@
         <v>681</v>
       </c>
       <c r="C681" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="682" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11006,7 +11042,7 @@
         <v>682</v>
       </c>
       <c r="C682" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="683" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11017,7 +11053,7 @@
         <v>683</v>
       </c>
       <c r="C683" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="684" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11028,7 +11064,7 @@
         <v>684</v>
       </c>
       <c r="C684" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="685" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11039,7 +11075,7 @@
         <v>685</v>
       </c>
       <c r="C685" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="686" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11050,7 +11086,7 @@
         <v>686</v>
       </c>
       <c r="C686" s="1">
-        <v>8.9700000000000006</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="687" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11061,7 +11097,7 @@
         <v>687</v>
       </c>
       <c r="C687" s="1">
-        <v>8.9700000000000006</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="688" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11072,7 +11108,7 @@
         <v>688</v>
       </c>
       <c r="C688" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="689" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11083,7 +11119,7 @@
         <v>689</v>
       </c>
       <c r="C689" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="690" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11094,7 +11130,7 @@
         <v>690</v>
       </c>
       <c r="C690" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="691" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11105,7 +11141,7 @@
         <v>691</v>
       </c>
       <c r="C691" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="692" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11116,7 +11152,7 @@
         <v>692</v>
       </c>
       <c r="C692" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="693" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11127,7 +11163,7 @@
         <v>693</v>
       </c>
       <c r="C693" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="694" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11138,7 +11174,7 @@
         <v>694</v>
       </c>
       <c r="C694" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="695" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11149,7 +11185,7 @@
         <v>695</v>
       </c>
       <c r="C695" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="696" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11160,7 +11196,7 @@
         <v>696</v>
       </c>
       <c r="C696" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="697" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11171,7 +11207,7 @@
         <v>697</v>
       </c>
       <c r="C697" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="698" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11182,7 +11218,7 @@
         <v>698</v>
       </c>
       <c r="C698" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="699" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11193,7 +11229,7 @@
         <v>699</v>
       </c>
       <c r="C699" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="700" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11204,7 +11240,7 @@
         <v>700</v>
       </c>
       <c r="C700" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="701" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11215,7 +11251,7 @@
         <v>701</v>
       </c>
       <c r="C701" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="702" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11226,7 +11262,7 @@
         <v>702</v>
       </c>
       <c r="C702" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="703" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11237,7 +11273,7 @@
         <v>703</v>
       </c>
       <c r="C703" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="704" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11248,7 +11284,7 @@
         <v>704</v>
       </c>
       <c r="C704" s="1">
-        <v>7.41</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="705" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11259,7 +11295,7 @@
         <v>705</v>
       </c>
       <c r="C705" s="1">
-        <v>7.41</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="706" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11270,7 +11306,7 @@
         <v>706</v>
       </c>
       <c r="C706" s="1">
-        <v>8.32</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="707" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11281,7 +11317,7 @@
         <v>707</v>
       </c>
       <c r="C707" s="1">
-        <v>8.32</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="708" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11292,7 +11328,7 @@
         <v>708</v>
       </c>
       <c r="C708" s="1">
-        <v>8.32</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="709" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11303,7 +11339,7 @@
         <v>709</v>
       </c>
       <c r="C709" s="1">
-        <v>8.32</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="710" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11314,7 +11350,7 @@
         <v>710</v>
       </c>
       <c r="C710" s="1">
-        <v>8.32</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="711" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11325,7 +11361,7 @@
         <v>711</v>
       </c>
       <c r="C711" s="1">
-        <v>8.32</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="712" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11490,7 +11526,7 @@
         <v>726</v>
       </c>
       <c r="C726" s="1">
-        <v>5.48</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11501,7 +11537,7 @@
         <v>727</v>
       </c>
       <c r="C727" s="1">
-        <v>5.48</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11512,7 +11548,7 @@
         <v>728</v>
       </c>
       <c r="C728" s="1">
-        <v>5.48</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11523,7 +11559,7 @@
         <v>729</v>
       </c>
       <c r="C729" s="1">
-        <v>5.48</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="730" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11534,7 +11570,7 @@
         <v>730</v>
       </c>
       <c r="C730" s="1">
-        <v>8.32</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11545,7 +11581,7 @@
         <v>731</v>
       </c>
       <c r="C731" s="1">
-        <v>8.32</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11556,7 +11592,7 @@
         <v>732</v>
       </c>
       <c r="C732" s="1">
-        <v>8.32</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11567,7 +11603,7 @@
         <v>733</v>
       </c>
       <c r="C733" s="1">
-        <v>8.32</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11578,7 +11614,7 @@
         <v>734</v>
       </c>
       <c r="C734" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11589,7 +11625,7 @@
         <v>735</v>
       </c>
       <c r="C735" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11600,7 +11636,7 @@
         <v>736</v>
       </c>
       <c r="C736" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11611,7 +11647,7 @@
         <v>737</v>
       </c>
       <c r="C737" s="1">
-        <v>8.32</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="738" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11622,7 +11658,7 @@
         <v>738</v>
       </c>
       <c r="C738" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="739" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11633,7 +11669,7 @@
         <v>739</v>
       </c>
       <c r="C739" s="1">
-        <v>7.41</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="740" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11842,7 +11878,7 @@
         <v>758</v>
       </c>
       <c r="C758" s="1">
-        <v>7.41</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="759" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11853,7 +11889,7 @@
         <v>759</v>
       </c>
       <c r="C759" s="1">
-        <v>7.41</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="760" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11864,7 +11900,7 @@
         <v>760</v>
       </c>
       <c r="C760" s="1">
-        <v>7.41</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="761" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11875,7 +11911,7 @@
         <v>761</v>
       </c>
       <c r="C761" s="1">
-        <v>7.41</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="762" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11886,7 +11922,7 @@
         <v>762</v>
       </c>
       <c r="C762" s="1">
-        <v>11.52</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="763" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11897,7 +11933,7 @@
         <v>763</v>
       </c>
       <c r="C763" s="1">
-        <v>11.52</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="764" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11908,7 +11944,7 @@
         <v>764</v>
       </c>
       <c r="C764" s="1">
-        <v>6.78</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="765" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11919,7 +11955,7 @@
         <v>765</v>
       </c>
       <c r="C765" s="1">
-        <v>6.78</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="766" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11930,7 +11966,7 @@
         <v>766</v>
       </c>
       <c r="C766" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="767" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11941,7 +11977,7 @@
         <v>767</v>
       </c>
       <c r="C767" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="768" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11952,7 +11988,7 @@
         <v>768</v>
       </c>
       <c r="C768" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="769" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11963,7 +11999,7 @@
         <v>769</v>
       </c>
       <c r="C769" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="770" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11974,7 +12010,7 @@
         <v>770</v>
       </c>
       <c r="C770" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="771" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11985,7 +12021,7 @@
         <v>771</v>
       </c>
       <c r="C771" s="1">
-        <v>9.48</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="772" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11996,7 +12032,7 @@
         <v>772</v>
       </c>
       <c r="C772" s="1">
-        <v>9.48</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="773" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12007,7 +12043,7 @@
         <v>773</v>
       </c>
       <c r="C773" s="1">
-        <v>9.48</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="774" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12018,7 +12054,7 @@
         <v>774</v>
       </c>
       <c r="C774" s="1">
-        <v>9.48</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="775" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12029,7 +12065,7 @@
         <v>775</v>
       </c>
       <c r="C775" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12040,7 +12076,7 @@
         <v>776</v>
       </c>
       <c r="C776" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12051,7 +12087,7 @@
         <v>777</v>
       </c>
       <c r="C777" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="778" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12062,7 +12098,7 @@
         <v>778</v>
       </c>
       <c r="C778" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="779" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12073,7 +12109,7 @@
         <v>779</v>
       </c>
       <c r="C779" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
     </row>
     <row r="780" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12084,7 +12120,7 @@
         <v>780</v>
       </c>
       <c r="C780" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="781" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12095,7 +12131,7 @@
         <v>781</v>
       </c>
       <c r="C781" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="782" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12106,7 +12142,7 @@
         <v>782</v>
       </c>
       <c r="C782" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="783" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12117,7 +12153,7 @@
         <v>783</v>
       </c>
       <c r="C783" s="1">
-        <v>8.9700000000000006</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="784" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12172,7 +12208,7 @@
         <v>788</v>
       </c>
       <c r="C788" s="1">
-        <v>9.61</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="789" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12183,7 +12219,7 @@
         <v>789</v>
       </c>
       <c r="C789" s="1">
-        <v>9.61</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="790" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12194,7 +12230,7 @@
         <v>790</v>
       </c>
       <c r="C790" s="1">
-        <v>9.61</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="791" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12205,7 +12241,7 @@
         <v>791</v>
       </c>
       <c r="C791" s="1">
-        <v>9.61</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="792" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12216,7 +12252,7 @@
         <v>792</v>
       </c>
       <c r="C792" s="1">
-        <v>7.68</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="793" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12304,7 +12340,7 @@
         <v>800</v>
       </c>
       <c r="C800" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="801" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12315,7 +12351,7 @@
         <v>801</v>
       </c>
       <c r="C801" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="802" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12326,7 +12362,7 @@
         <v>802</v>
       </c>
       <c r="C802" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="803" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12337,7 +12373,7 @@
         <v>803</v>
       </c>
       <c r="C803" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="804" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12348,7 +12384,7 @@
         <v>804</v>
       </c>
       <c r="C804" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="805" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12359,7 +12395,7 @@
         <v>805</v>
       </c>
       <c r="C805" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="806" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12370,7 +12406,7 @@
         <v>806</v>
       </c>
       <c r="C806" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="807" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12381,7 +12417,7 @@
         <v>807</v>
       </c>
       <c r="C807" s="1">
-        <v>11.94</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="808" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12392,7 +12428,7 @@
         <v>808</v>
       </c>
       <c r="C808" s="1">
-        <v>11.94</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="809" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12403,7 +12439,7 @@
         <v>809</v>
       </c>
       <c r="C809" s="1">
-        <v>11.94</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="810" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12414,7 +12450,7 @@
         <v>810</v>
       </c>
       <c r="C810" s="1">
-        <v>11.94</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="811" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12425,7 +12461,7 @@
         <v>811</v>
       </c>
       <c r="C811" s="1">
-        <v>11.94</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="812" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12447,7 +12483,7 @@
         <v>813</v>
       </c>
       <c r="C813" s="1">
-        <v>9.24</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="814" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12458,7 +12494,7 @@
         <v>814</v>
       </c>
       <c r="C814" s="1">
-        <v>10.84</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="815" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12469,7 +12505,7 @@
         <v>815</v>
       </c>
       <c r="C815" s="1">
-        <v>11.54</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="816" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12480,7 +12516,7 @@
         <v>816</v>
       </c>
       <c r="C816" s="1">
-        <v>11.54</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="817" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12491,7 +12527,7 @@
         <v>817</v>
       </c>
       <c r="C817" s="1">
-        <v>11.54</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="818" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12524,7 +12560,7 @@
         <v>820</v>
       </c>
       <c r="C820" s="1">
-        <v>12.84</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="821" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12535,7 +12571,7 @@
         <v>821</v>
       </c>
       <c r="C821" s="1">
-        <v>12.84</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="822" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12546,7 +12582,7 @@
         <v>822</v>
       </c>
       <c r="C822" s="1">
-        <v>12.84</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="823" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12557,7 +12593,7 @@
         <v>823</v>
       </c>
       <c r="C823" s="1">
-        <v>12.84</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="824" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12579,7 +12615,7 @@
         <v>825</v>
       </c>
       <c r="C825" s="1">
-        <v>12.84</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="826" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12678,7 +12714,7 @@
         <v>834</v>
       </c>
       <c r="C834" s="1">
-        <v>12.84</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12689,7 +12725,7 @@
         <v>835</v>
       </c>
       <c r="C835" s="1">
-        <v>12.84</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="836" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12700,7 +12736,7 @@
         <v>836</v>
       </c>
       <c r="C836" s="1">
-        <v>12.84</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="837" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12711,7 +12747,7 @@
         <v>837</v>
       </c>
       <c r="C837" s="1">
-        <v>12.84</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12722,7 +12758,7 @@
         <v>838</v>
       </c>
       <c r="C838" s="1">
-        <v>10.48</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12733,7 +12769,7 @@
         <v>839</v>
       </c>
       <c r="C839" s="1">
-        <v>11.94</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12788,7 +12824,7 @@
         <v>844</v>
       </c>
       <c r="C844" s="1">
-        <v>15.4</v>
+        <v>35.479999999999997</v>
       </c>
     </row>
     <row r="845" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12799,7 +12835,7 @@
         <v>845</v>
       </c>
       <c r="C845" s="1">
-        <v>15.4</v>
+        <v>35.479999999999997</v>
       </c>
     </row>
     <row r="846" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12810,7 +12846,7 @@
         <v>846</v>
       </c>
       <c r="C846" s="1">
-        <v>15.4</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="847" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12821,7 +12857,7 @@
         <v>847</v>
       </c>
       <c r="C847" s="1">
-        <v>15.4</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="848" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12832,7 +12868,7 @@
         <v>848</v>
       </c>
       <c r="C848" s="1">
-        <v>35.479999999999997</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="849" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12843,7 +12879,7 @@
         <v>849</v>
       </c>
       <c r="C849" s="1">
-        <v>35.479999999999997</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="850" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12865,7 +12901,7 @@
         <v>851</v>
       </c>
       <c r="C851" s="1">
-        <v>23.16</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="852" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12876,7 +12912,7 @@
         <v>852</v>
       </c>
       <c r="C852" s="1">
-        <v>23.16</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="853" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12898,7 +12934,7 @@
         <v>854</v>
       </c>
       <c r="C854" s="1">
-        <v>23.16</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="855" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12964,7 +13000,7 @@
         <v>860</v>
       </c>
       <c r="C860" s="1">
-        <v>24.45</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="861" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12975,15 +13011,15 @@
         <v>861</v>
       </c>
       <c r="C861" s="1">
-        <v>24.45</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="862" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
-        <v>862</v>
+        <v>1068</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>862</v>
+        <v>1068</v>
       </c>
       <c r="C862" s="1">
         <v>24.45</v>
@@ -12991,10 +13027,10 @@
     </row>
     <row r="863" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
-        <v>863</v>
+        <v>1069</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>863</v>
+        <v>1069</v>
       </c>
       <c r="C863" s="1">
         <v>24.45</v>
@@ -13002,10 +13038,10 @@
     </row>
     <row r="864" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
-        <v>864</v>
+        <v>1070</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>864</v>
+        <v>1070</v>
       </c>
       <c r="C864" s="1">
         <v>24.45</v>
@@ -13013,252 +13049,252 @@
     </row>
     <row r="865" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C865" s="1">
-        <v>24.45</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="866" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C866" s="1">
-        <v>23.16</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="867" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B867" s="1" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C867" s="1">
-        <v>23.16</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="868" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="1" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C868" s="1">
-        <v>23.16</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="869" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
-        <v>869</v>
+        <v>1071</v>
       </c>
       <c r="B869" s="1" t="s">
-        <v>869</v>
+        <v>1071</v>
       </c>
       <c r="C869" s="1">
-        <v>23.16</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="870" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
-        <v>870</v>
+        <v>1072</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>870</v>
+        <v>1072</v>
       </c>
       <c r="C870" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="871" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
-        <v>871</v>
+        <v>1072</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>871</v>
+        <v>1072</v>
       </c>
       <c r="C871" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="872" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
-        <v>872</v>
+        <v>1073</v>
       </c>
       <c r="B872" s="1" t="s">
-        <v>872</v>
+        <v>1073</v>
       </c>
       <c r="C872" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="873" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
-        <v>873</v>
+        <v>1074</v>
       </c>
       <c r="B873" s="1" t="s">
-        <v>873</v>
+        <v>1074</v>
       </c>
       <c r="C873" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="874" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
-        <v>874</v>
+        <v>1075</v>
       </c>
       <c r="B874" s="1" t="s">
-        <v>874</v>
+        <v>1075</v>
       </c>
       <c r="C874" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="875" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
-        <v>875</v>
+        <v>1076</v>
       </c>
       <c r="B875" s="1" t="s">
-        <v>875</v>
+        <v>1076</v>
       </c>
       <c r="C875" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="876" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
-        <v>876</v>
+        <v>1077</v>
       </c>
       <c r="B876" s="1" t="s">
-        <v>876</v>
+        <v>1077</v>
       </c>
       <c r="C876" s="1">
-        <v>12.19</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="877" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="B877" s="1" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="C877" s="1">
-        <v>12.19</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="878" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="B878" s="1" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="C878" s="1">
-        <v>12.19</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="879" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="B879" s="1" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="C879" s="1">
-        <v>12.19</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="880" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="1" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="B880" s="1" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="C880" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="881" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="1" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="B881" s="1" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="C881" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="882" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="1" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="B882" s="1" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="C882" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="883" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="1" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="B883" s="1" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="C883" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="884" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="1" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B884" s="1" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="C884" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="885" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="1" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
       <c r="B885" s="1" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
       <c r="C885" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="886" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="1" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="B886" s="1" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="C886" s="1">
-        <v>21.29</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="887" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="1" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="B887" s="1" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="C887" s="1">
         <v>21.29</v>
@@ -13266,21 +13302,21 @@
     </row>
     <row r="888" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="1" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="C888" s="1">
-        <v>21.29</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="889" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="1" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="B889" s="1" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="C889" s="1">
         <v>21.29</v>
@@ -13288,10 +13324,10 @@
     </row>
     <row r="890" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="1" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B890" s="1" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="C890" s="1">
         <v>21.29</v>
@@ -13299,10 +13335,10 @@
     </row>
     <row r="891" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="1" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="B891" s="1" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C891" s="1">
         <v>21.29</v>
@@ -13310,10 +13346,10 @@
     </row>
     <row r="892" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="1" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="B892" s="1" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="C892" s="1">
         <v>21.29</v>
@@ -13321,10 +13357,10 @@
     </row>
     <row r="893" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="1" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="B893" s="1" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="C893" s="1">
         <v>21.29</v>
@@ -13332,10 +13368,10 @@
     </row>
     <row r="894" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="1" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="B894" s="1" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="C894" s="1">
         <v>21.29</v>
@@ -13343,10 +13379,10 @@
     </row>
     <row r="895" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="1" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="B895" s="1" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="C895" s="1">
         <v>21.29</v>
@@ -13354,10 +13390,10 @@
     </row>
     <row r="896" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="1" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="B896" s="1" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="C896" s="1">
         <v>21.29</v>
@@ -13365,10 +13401,10 @@
     </row>
     <row r="897" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="1" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="B897" s="1" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="C897" s="1">
         <v>21.29</v>
@@ -13376,131 +13412,131 @@
     </row>
     <row r="898" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="1" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="B898" s="1" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="C898" s="1">
-        <v>5.0999999999999996</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="1" t="s">
-        <v>1071</v>
+        <v>888</v>
       </c>
       <c r="B899" s="1" t="s">
-        <v>1071</v>
+        <v>888</v>
       </c>
       <c r="C899" s="1">
-        <v>5.8</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="900" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="1" t="s">
-        <v>1072</v>
+        <v>889</v>
       </c>
       <c r="B900" s="1" t="s">
-        <v>1072</v>
+        <v>889</v>
       </c>
       <c r="C900" s="1">
-        <v>14.15</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="901" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="1" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B901" s="1" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C901" s="1">
-        <v>2.76</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="1" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="B902" s="1" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="C902" s="1">
-        <v>2.76</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="903" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="1" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="B903" s="1" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="C903" s="1">
-        <v>5.15</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="1" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="B904" s="1" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="C904" s="1">
-        <v>5.15</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="905" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="1" t="s">
-        <v>903</v>
+        <v>1066</v>
       </c>
       <c r="B905" s="1" t="s">
-        <v>903</v>
+        <v>1066</v>
       </c>
       <c r="C905" s="1">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="906" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="1" t="s">
-        <v>904</v>
+        <v>1067</v>
       </c>
       <c r="B906" s="1" t="s">
-        <v>904</v>
+        <v>1067</v>
       </c>
       <c r="C906" s="1">
-        <v>5.15</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="907" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="1" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B907" s="1" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="C907" s="1">
-        <v>5.15</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="908" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="1" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="B908" s="1" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="C908" s="1">
-        <v>5.15</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="909" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="1" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="B909" s="1" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="C909" s="1">
         <v>5.15</v>
@@ -13508,10 +13544,10 @@
     </row>
     <row r="910" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="1" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="B910" s="1" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="C910" s="1">
         <v>5.15</v>
@@ -13519,120 +13555,120 @@
     </row>
     <row r="911" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="1" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="C911" s="1">
-        <v>6.39</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="912" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="1" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="B912" s="1" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="C912" s="1">
-        <v>6.39</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="913" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="1" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="B913" s="1" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="C913" s="1">
-        <v>7.41</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="914" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="1" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="B914" s="1" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="C914" s="1">
-        <v>7.41</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="915" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="1" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="B915" s="1" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="C915" s="1">
-        <v>17.36</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="916" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="1" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B916" s="1" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="C916" s="1">
-        <v>17.36</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="917" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="1" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="B917" s="1" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="C917" s="1">
-        <v>17.36</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="918" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="1" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="B918" s="1" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="C918" s="1">
-        <v>5.16</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="919" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="1" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="B919" s="1" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="C919" s="1">
-        <v>5.16</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="920" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="1" t="s">
-        <v>918</v>
+        <v>907</v>
       </c>
       <c r="B920" s="1" t="s">
-        <v>918</v>
+        <v>907</v>
       </c>
       <c r="C920" s="1">
-        <v>5.16</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="921" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="1" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="B921" s="1" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="C921" s="1">
         <v>17.36</v>
@@ -13640,10 +13676,10 @@
     </row>
     <row r="922" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="1" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="B922" s="1" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="C922" s="1">
         <v>17.36</v>
@@ -13651,10 +13687,10 @@
     </row>
     <row r="923" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="1" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="B923" s="1" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="C923" s="1">
         <v>17.36</v>
@@ -13662,10 +13698,10 @@
     </row>
     <row r="924" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="1" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="B924" s="1" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="C924" s="1">
         <v>5.16</v>
@@ -13673,10 +13709,10 @@
     </row>
     <row r="925" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="1" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="B925" s="1" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="C925" s="1">
         <v>5.16</v>
@@ -13684,10 +13720,10 @@
     </row>
     <row r="926" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="1" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="B926" s="1" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="C926" s="1">
         <v>5.16</v>
@@ -13695,76 +13731,76 @@
     </row>
     <row r="927" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="1" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
       <c r="B927" s="1" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
       <c r="C927" s="1">
-        <v>6.45</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="928" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="1" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="B928" s="1" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="C928" s="1">
-        <v>6.45</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="929" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="1" t="s">
-        <v>927</v>
+        <v>916</v>
       </c>
       <c r="B929" s="1" t="s">
-        <v>927</v>
+        <v>916</v>
       </c>
       <c r="C929" s="1">
-        <v>6.45</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="930" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="1" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="B930" s="1" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="C930" s="1">
-        <v>16.059999999999999</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="931" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="1" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="B931" s="1" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="C931" s="1">
-        <v>16.059999999999999</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="932" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="1" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="B932" s="1" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="C932" s="1">
-        <v>16.059999999999999</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="933" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="1" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="B933" s="1" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="C933" s="1">
         <v>6.45</v>
@@ -13772,175 +13808,175 @@
     </row>
     <row r="934" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="1" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="B934" s="1" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="C934" s="1">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="935" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="1" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="B935" s="1" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="C935" s="1">
-        <v>1.6</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="936" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="1" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="B936" s="1" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="C936" s="1">
-        <v>7.2</v>
+        <v>16.059999999999999</v>
       </c>
     </row>
     <row r="937" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="1" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="B937" s="1" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="C937" s="1">
-        <v>1.6</v>
+        <v>16.059999999999999</v>
       </c>
     </row>
     <row r="938" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="1" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="B938" s="1" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="C938" s="1">
-        <v>7.2</v>
+        <v>16.059999999999999</v>
       </c>
     </row>
     <row r="939" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="1" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="B939" s="1" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="C939" s="1">
-        <v>1.6</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="940" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="1" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="B940" s="1" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="C940" s="1">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="941" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="1" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="B941" s="1" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="C941" s="1">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="942" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="1" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="B942" s="1" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="C942" s="1">
-        <v>6.66</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="943" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="1" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="B943" s="1" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="C943" s="1">
-        <v>3.22</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="944" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="1" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
       <c r="B944" s="1" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
       <c r="C944" s="1">
-        <v>3.22</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="945" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="1" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="B945" s="1" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="C945" s="1">
-        <v>3.22</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="946" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="1" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="B946" s="1" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="C946" s="1">
-        <v>3.22</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="947" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="1" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="B947" s="1" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="C947" s="1">
-        <v>3.22</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="948" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="1" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="B948" s="1" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="C948" s="1">
-        <v>3.22</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="949" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="1" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="C949" s="1">
         <v>3.22</v>
@@ -13948,109 +13984,109 @@
     </row>
     <row r="950" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="1" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="C950" s="1">
-        <v>0.75</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="1" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="B951" s="1" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="C951" s="1">
-        <v>0.72</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="1" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="B952" s="1" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="C952" s="1">
-        <v>1.0960000000000001</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="953" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="1" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="B953" s="1" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="C953" s="1">
-        <v>1.0960000000000001</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="1" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="B954" s="1" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="C954" s="1">
-        <v>0.72</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="1" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="B955" s="1" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="C955" s="1">
-        <v>3.8079999999999998</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="956" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="1" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="B956" s="1" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="C956" s="1">
-        <v>3.8079999999999998</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="1" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="B957" s="1" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="C957" s="1">
-        <v>3.8079999999999998</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="958" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="1" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="B958" s="1" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="C958" s="1">
-        <v>3.8079999999999998</v>
+        <v>1.0960000000000001</v>
       </c>
     </row>
     <row r="959" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="1" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="B959" s="1" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="C959" s="1">
         <v>1.0960000000000001</v>
@@ -14058,351 +14094,351 @@
     </row>
     <row r="960" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="1" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="B960" s="1" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="C960" s="1">
-        <v>1.0960000000000001</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="961" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="1" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="B961" s="1" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C961" s="1">
-        <v>8.6</v>
+        <v>3.8079999999999998</v>
       </c>
     </row>
     <row r="962" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="1" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="B962" s="1" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="C962" s="1">
-        <v>18</v>
+        <v>3.8079999999999998</v>
       </c>
     </row>
     <row r="963" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="1" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="B963" s="1" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="C963" s="1">
-        <v>5.82</v>
+        <v>3.8079999999999998</v>
       </c>
     </row>
     <row r="964" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="1" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="B964" s="1" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="C964" s="1">
-        <v>5.82</v>
+        <v>3.8079999999999998</v>
       </c>
     </row>
     <row r="965" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="1" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="B965" s="1" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="C965" s="1">
-        <v>4.96</v>
+        <v>1.0960000000000001</v>
       </c>
     </row>
     <row r="966" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="1" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="B966" s="1" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="C966" s="1">
-        <v>4.41</v>
+        <v>1.0960000000000001</v>
       </c>
     </row>
     <row r="967" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="1" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="B967" s="1" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="C967" s="1">
-        <v>4.41</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="968" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="1" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B968" s="1" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="C968" s="1">
-        <v>11.61</v>
+        <v>18</v>
       </c>
     </row>
     <row r="969" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="1" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="B969" s="1" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="C969" s="1">
-        <v>10.904</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="970" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="1" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="B970" s="1" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="C970" s="1">
-        <v>10.904</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="971" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="1" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="B971" s="1" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="C971" s="1">
-        <v>10.904</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="972" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="1" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="B972" s="1" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="C972" s="1">
-        <v>10.26</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="973" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="B973" s="1" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="C973" s="1">
-        <v>10.26</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="974" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="1" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="B974" s="1" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="C974" s="1">
-        <v>16.064</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="975" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="1" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="B975" s="1" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="C975" s="1">
-        <v>16.064</v>
+        <v>10.904</v>
       </c>
     </row>
     <row r="976" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="1" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="B976" s="1" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="C976" s="1">
-        <v>16.064</v>
+        <v>10.904</v>
       </c>
     </row>
     <row r="977" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="1" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="B977" s="1" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="C977" s="1">
-        <v>16.064</v>
+        <v>10.904</v>
       </c>
     </row>
     <row r="978" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="1" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="B978" s="1" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="C978" s="1">
-        <v>10.256</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="979" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="1" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="B979" s="1" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="C979" s="1">
-        <v>10.256</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="980" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="1" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="B980" s="1" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="C980" s="1">
-        <v>10.256</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="981" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="1" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="B981" s="1" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="C981" s="1">
-        <v>6.4</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="982" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="1" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="B982" s="1" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="C982" s="1">
-        <v>5.2</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="983" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="1" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="B983" s="1" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="C983" s="1">
-        <v>5.2</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="984" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="1" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="B984" s="1" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="C984" s="1">
-        <v>5.5279999999999996</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="985" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="1" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="B985" s="1" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="C985" s="1">
-        <v>6.38</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="986" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="1" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="B986" s="1" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="C986" s="1">
-        <v>6.38</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="987" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="1" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="B987" s="1" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="C987" s="1">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="988" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="1" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="B988" s="1" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="C988" s="1">
-        <v>6.38</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="989" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="1" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
       <c r="B989" s="1" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
       <c r="C989" s="1">
-        <v>6.38</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="990" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="1" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="B990" s="1" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="C990" s="1">
-        <v>6.38</v>
+        <v>5.5279999999999996</v>
       </c>
     </row>
     <row r="991" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="1" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="B991" s="1" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="C991" s="1">
         <v>6.38</v>
@@ -14410,824 +14446,824 @@
     </row>
     <row r="992" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="1" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="B992" s="1" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="C992" s="1">
-        <v>7.7279999999999998</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="993" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="1" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="C993" s="1">
-        <v>7.7279999999999998</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="994" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="1" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="B994" s="1" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="C994" s="1">
-        <v>8.968</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="995" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="1" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="B995" s="1" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="C995" s="1">
-        <v>8.968</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="996" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="1" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
       <c r="B996" s="1" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
       <c r="C996" s="1">
-        <v>8.968</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="997" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="1" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="B997" s="1" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="C997" s="1">
-        <v>8.968</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="998" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="1" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="B998" s="1" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="C998" s="1">
-        <v>6</v>
+        <v>7.7279999999999998</v>
       </c>
     </row>
     <row r="999" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="1" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="B999" s="1" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="C999" s="1">
-        <v>6</v>
+        <v>7.7279999999999998</v>
       </c>
     </row>
     <row r="1000" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="1" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="B1000" s="1" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="C1000" s="1">
-        <v>6</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1001" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="1" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="B1001" s="1" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="C1001" s="1">
-        <v>15.91</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1002" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="1" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="B1002" s="1" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="C1002" s="1">
-        <v>5.74</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1003" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="1" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="B1003" s="1" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="C1003" s="1">
-        <v>22.576000000000001</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1004" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="1" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
       <c r="B1004" s="1" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
       <c r="C1004" s="1">
-        <v>16.064</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1005" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="1" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="B1005" s="1" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="C1005" s="1">
-        <v>16.064</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1006" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="1" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="B1006" s="1" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="C1006" s="1">
-        <v>16.064</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1007" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="1" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="B1007" s="1" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="C1007" s="1">
-        <v>12.832000000000001</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="1008" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="1" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="B1008" s="1" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="C1008" s="1">
-        <v>12.832000000000001</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="1009" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="1" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="B1009" s="1" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="C1009" s="1">
-        <v>12.832000000000001</v>
+        <v>22.576000000000001</v>
       </c>
     </row>
     <row r="1010" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="1" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="B1010" s="1" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="C1010" s="1">
-        <v>13.12</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="1011" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="1" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="B1011" s="1" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="C1011" s="1">
-        <v>13.12</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="1012" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="1" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="B1012" s="1" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="C1012" s="1">
-        <v>13.12</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="1013" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="1" t="s">
-        <v>1011</v>
+        <v>1000</v>
       </c>
       <c r="B1013" s="1" t="s">
-        <v>1011</v>
+        <v>1000</v>
       </c>
       <c r="C1013" s="1">
-        <v>13.12</v>
+        <v>12.832000000000001</v>
       </c>
     </row>
     <row r="1014" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="1" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="B1014" s="1" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="C1014" s="1">
-        <v>13.12</v>
+        <v>12.832000000000001</v>
       </c>
     </row>
     <row r="1015" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="1" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
       <c r="B1015" s="1" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
       <c r="C1015" s="1">
-        <v>13.12</v>
+        <v>12.832000000000001</v>
       </c>
     </row>
     <row r="1016" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="1" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
       <c r="B1016" s="1" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
       <c r="C1016" s="1">
-        <v>13.79</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="1" t="s">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="B1017" s="1" t="s">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="C1017" s="1">
-        <v>19.7</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1018" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="1" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
       <c r="B1018" s="1" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
       <c r="C1018" s="1">
-        <v>14.128</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1019" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="1" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
       <c r="B1019" s="1" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
       <c r="C1019" s="1">
-        <v>5.7359999999999998</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="1" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
       <c r="B1020" s="1" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
       <c r="C1020" s="1">
-        <v>5.7359999999999998</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1021" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="1" t="s">
-        <v>1019</v>
+        <v>1008</v>
       </c>
       <c r="B1021" s="1" t="s">
-        <v>1019</v>
+        <v>1008</v>
       </c>
       <c r="C1021" s="1">
-        <v>5.7359999999999998</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="1" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
       <c r="B1022" s="1" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
       <c r="C1022" s="1">
-        <v>5.7359999999999998</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="1023" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="1" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="B1023" s="1" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="C1023" s="1">
-        <v>5.0960000000000001</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="1024" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="1" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="B1024" s="1" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="C1024" s="1">
-        <v>6.3840000000000003</v>
+        <v>14.128</v>
       </c>
     </row>
     <row r="1025" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="1" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
       <c r="B1025" s="1" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
       <c r="C1025" s="1">
-        <v>7.6719999999999997</v>
+        <v>5.7359999999999998</v>
       </c>
     </row>
     <row r="1026" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="1" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
       <c r="B1026" s="1" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
       <c r="C1026" s="1">
-        <v>8.9600000000000009</v>
+        <v>5.7359999999999998</v>
       </c>
     </row>
     <row r="1027" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="1" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
       <c r="B1027" s="1" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
       <c r="C1027" s="1">
-        <v>6.1760000000000002</v>
+        <v>5.7359999999999998</v>
       </c>
     </row>
     <row r="1028" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="1" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="B1028" s="1" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="C1028" s="1">
-        <v>6.1760000000000002</v>
+        <v>5.7359999999999998</v>
       </c>
     </row>
     <row r="1029" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="1" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="B1029" s="1" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="C1029" s="1">
-        <v>6.1760000000000002</v>
+        <v>5.0960000000000001</v>
       </c>
     </row>
     <row r="1030" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="1" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="B1030" s="1" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="C1030" s="1">
-        <v>7.992</v>
+        <v>6.3840000000000003</v>
       </c>
     </row>
     <row r="1031" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="1" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="B1031" s="1" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="C1031" s="1">
-        <v>7.992</v>
+        <v>7.6719999999999997</v>
       </c>
     </row>
     <row r="1032" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="1" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="B1032" s="1" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="C1032" s="1">
-        <v>7.992</v>
+        <v>8.9600000000000009</v>
       </c>
     </row>
     <row r="1033" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="1" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
       <c r="B1033" s="1" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
       <c r="C1033" s="1">
-        <v>10</v>
+        <v>6.1760000000000002</v>
       </c>
     </row>
     <row r="1034" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="1" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
       <c r="B1034" s="1" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
       <c r="C1034" s="1">
-        <v>10</v>
+        <v>6.1760000000000002</v>
       </c>
     </row>
     <row r="1035" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="1" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
       <c r="B1035" s="1" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
       <c r="C1035" s="1">
-        <v>10</v>
+        <v>6.1760000000000002</v>
       </c>
     </row>
     <row r="1036" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="1" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="B1036" s="1" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="C1036" s="1">
-        <v>167.98</v>
+        <v>7.992</v>
       </c>
     </row>
     <row r="1037" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="1" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
       <c r="B1037" s="1" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
       <c r="C1037" s="1">
-        <v>10.4</v>
+        <v>7.992</v>
       </c>
     </row>
     <row r="1038" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="1" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
       <c r="B1038" s="1" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
       <c r="C1038" s="1">
-        <v>58.24</v>
+        <v>7.992</v>
       </c>
     </row>
     <row r="1039" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="1" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
       <c r="B1039" s="1" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
       <c r="C1039" s="1">
-        <v>7.41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1040" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="1" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
       <c r="B1040" s="1" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
       <c r="C1040" s="1">
-        <v>7.41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1041" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="1" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="B1041" s="1" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="C1041" s="1">
-        <v>7.41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1042" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="1" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
       <c r="B1042" s="1" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
       <c r="C1042" s="1">
-        <v>7.41</v>
+        <v>167.98</v>
       </c>
     </row>
     <row r="1043" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="1" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="B1043" s="1" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="C1043" s="1">
-        <v>7.41</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="1044" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="1" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="B1044" s="1" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="C1044" s="1">
-        <v>10.8</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="1045" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="1" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="B1045" s="1" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="C1045" s="1">
-        <v>10.8</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1046" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="1" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
       <c r="B1046" s="1" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
       <c r="C1046" s="1">
-        <v>10.8</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1047" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="1" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
       <c r="B1047" s="1" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
       <c r="C1047" s="1">
-        <v>10.8</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1048" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="1" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="B1048" s="1" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="C1048" s="1">
-        <v>8.9</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1049" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="1" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
       <c r="B1049" s="1" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
       <c r="C1049" s="1">
-        <v>8.9</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1050" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="1" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
       <c r="B1050" s="1" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
       <c r="C1050" s="1">
-        <v>8.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="1051" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="1" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
       <c r="B1051" s="1" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
       <c r="C1051" s="1">
-        <v>8.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="1052" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1052" s="1" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
       <c r="B1052" s="1" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
       <c r="C1052" s="1">
-        <v>8.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="1053" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="1" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="B1053" s="1" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="C1053" s="1">
-        <v>8.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="1054" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="1" t="s">
-        <v>834</v>
+        <v>1041</v>
       </c>
       <c r="B1054" s="1" t="s">
-        <v>834</v>
+        <v>1041</v>
       </c>
       <c r="C1054" s="1">
-        <v>12.84</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1055" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1055" s="1" t="s">
-        <v>835</v>
+        <v>1042</v>
       </c>
       <c r="B1055" s="1" t="s">
-        <v>835</v>
+        <v>1042</v>
       </c>
       <c r="C1055" s="1">
-        <v>12.84</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1056" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1056" s="1" t="s">
-        <v>836</v>
+        <v>1043</v>
       </c>
       <c r="B1056" s="1" t="s">
-        <v>836</v>
+        <v>1043</v>
       </c>
       <c r="C1056" s="1">
-        <v>12.84</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1057" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="1" t="s">
-        <v>837</v>
+        <v>1044</v>
       </c>
       <c r="B1057" s="1" t="s">
-        <v>837</v>
+        <v>1044</v>
       </c>
       <c r="C1057" s="1">
-        <v>12.84</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1058" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1058" s="1" t="s">
-        <v>833</v>
+        <v>1045</v>
       </c>
       <c r="B1058" s="1" t="s">
-        <v>833</v>
+        <v>1045</v>
       </c>
       <c r="C1058" s="1">
-        <v>12.84</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1059" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1059" s="1" t="s">
-        <v>1069</v>
+        <v>1046</v>
       </c>
       <c r="B1059" s="1" t="s">
-        <v>1069</v>
+        <v>1046</v>
       </c>
       <c r="C1059" s="1">
-        <v>8.25</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1060" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1060" s="1" t="s">
-        <v>1052</v>
+        <v>830</v>
       </c>
       <c r="B1060" s="1" t="s">
-        <v>1052</v>
+        <v>830</v>
       </c>
       <c r="C1060" s="1">
-        <v>7.41</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="1061" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1061" s="1" t="s">
-        <v>1053</v>
+        <v>831</v>
       </c>
       <c r="B1061" s="1" t="s">
-        <v>1053</v>
+        <v>831</v>
       </c>
       <c r="C1061" s="1">
-        <v>7.41</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="1062" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1062" s="1" t="s">
-        <v>1054</v>
+        <v>832</v>
       </c>
       <c r="B1062" s="1" t="s">
-        <v>1054</v>
+        <v>832</v>
       </c>
       <c r="C1062" s="1">
-        <v>7.41</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="1063" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="1" t="s">
-        <v>1055</v>
+        <v>833</v>
       </c>
       <c r="B1063" s="1" t="s">
-        <v>1055</v>
+        <v>833</v>
       </c>
       <c r="C1063" s="1">
-        <v>7.41</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="1064" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="1" t="s">
-        <v>1056</v>
+        <v>829</v>
       </c>
       <c r="B1064" s="1" t="s">
-        <v>1056</v>
+        <v>829</v>
       </c>
       <c r="C1064" s="1">
-        <v>7.41</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="1065" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="B1065" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="C1065" s="1">
-        <v>7.41</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="1066" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="1" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
       <c r="B1066" s="1" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
       <c r="C1066" s="1">
         <v>7.41</v>
@@ -15235,10 +15271,10 @@
     </row>
     <row r="1067" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1067" s="1" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
       <c r="B1067" s="1" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
       <c r="C1067" s="1">
         <v>7.41</v>
@@ -15246,10 +15282,10 @@
     </row>
     <row r="1068" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1068" s="1" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="B1068" s="1" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="C1068" s="1">
         <v>7.41</v>
@@ -15257,10 +15293,10 @@
     </row>
     <row r="1069" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1069" s="1" t="s">
-        <v>1061</v>
+        <v>1050</v>
       </c>
       <c r="B1069" s="1" t="s">
-        <v>1061</v>
+        <v>1050</v>
       </c>
       <c r="C1069" s="1">
         <v>7.41</v>
@@ -15268,10 +15304,10 @@
     </row>
     <row r="1070" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1070" s="1" t="s">
-        <v>1062</v>
+        <v>1051</v>
       </c>
       <c r="B1070" s="1" t="s">
-        <v>1062</v>
+        <v>1051</v>
       </c>
       <c r="C1070" s="1">
         <v>7.41</v>
@@ -15279,10 +15315,10 @@
     </row>
     <row r="1071" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1071" s="1" t="s">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="B1071" s="1" t="s">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="C1071" s="1">
         <v>7.41</v>
@@ -15290,10 +15326,10 @@
     </row>
     <row r="1072" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1072" s="1" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="B1072" s="1" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="C1072" s="1">
         <v>7.41</v>
@@ -15301,10 +15337,10 @@
     </row>
     <row r="1073" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1073" s="1" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="B1073" s="1" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="C1073" s="1">
         <v>7.41</v>
@@ -15312,10 +15348,10 @@
     </row>
     <row r="1074" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1074" s="1" t="s">
-        <v>382</v>
+        <v>1055</v>
       </c>
       <c r="B1074" s="1" t="s">
-        <v>382</v>
+        <v>1055</v>
       </c>
       <c r="C1074" s="1">
         <v>7.41</v>
@@ -15323,10 +15359,10 @@
     </row>
     <row r="1075" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1075" s="1" t="s">
-        <v>384</v>
+        <v>1056</v>
       </c>
       <c r="B1075" s="1" t="s">
-        <v>384</v>
+        <v>1056</v>
       </c>
       <c r="C1075" s="1">
         <v>7.41</v>
@@ -15334,10 +15370,10 @@
     </row>
     <row r="1076" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1076" s="1" t="s">
-        <v>386</v>
+        <v>1057</v>
       </c>
       <c r="B1076" s="1" t="s">
-        <v>386</v>
+        <v>1057</v>
       </c>
       <c r="C1076" s="1">
         <v>7.41</v>
@@ -15345,10 +15381,10 @@
     </row>
     <row r="1077" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1077" s="1" t="s">
-        <v>389</v>
+        <v>1058</v>
       </c>
       <c r="B1077" s="1" t="s">
-        <v>389</v>
+        <v>1058</v>
       </c>
       <c r="C1077" s="1">
         <v>7.41</v>
@@ -15356,10 +15392,10 @@
     </row>
     <row r="1078" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1078" s="1" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="B1078" s="1" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="C1078" s="1">
         <v>7.41</v>
@@ -15367,10 +15403,10 @@
     </row>
     <row r="1079" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1079" s="1" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="B1079" s="1" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="C1079" s="1">
         <v>7.41</v>
@@ -15378,13 +15414,156 @@
     </row>
     <row r="1080" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="1" t="s">
-        <v>1068</v>
+        <v>382</v>
       </c>
       <c r="B1080" s="1" t="s">
-        <v>1068</v>
+        <v>382</v>
       </c>
       <c r="C1080" s="1">
         <v>7.41</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1081" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C1081" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1082" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1082" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1083" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1083" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B1084" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C1084" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B1085" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C1085" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B1086" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C1086" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1087" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C1087" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1088" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C1088" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1089" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C1089" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1090" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C1090" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1091" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C1091" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1092" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C1092" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1093" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C1093" s="1">
+        <v>13.65</v>
       </c>
     </row>
   </sheetData>

--- a/price-list-export.xlsx
+++ b/price-list-export.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Leeukopf-Website-Official\gelitup-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172CB0B9-D314-4A3E-9F5D-6DE2142CFC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFE5B35-C2BE-4464-A82C-16DBAC201BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="price-list-export" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="1088">
   <si>
     <t>Item Name</t>
   </si>
@@ -3275,6 +3275,15 @@
   </si>
   <si>
     <t>Neon Cat Eye #NCE07 -HTF</t>
+  </si>
+  <si>
+    <t>Premium Builder Gel Blue 20g -HTF</t>
+  </si>
+  <si>
+    <t>Premium Builder Gel Purple 20g -HTF</t>
+  </si>
+  <si>
+    <t>Premium Builder Gel Mint 20g -HTF</t>
   </si>
 </sst>
 </file>
@@ -9375,7 +9384,7 @@
     </row>
     <row r="531" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B531" s="1" t="s">
         <v>531</v>
@@ -13019,10 +13028,10 @@
         <v>1068</v>
       </c>
       <c r="B862" s="1" t="s">
-        <v>1068</v>
+        <v>1085</v>
       </c>
       <c r="C862" s="1">
-        <v>24.45</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="863" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13030,10 +13039,10 @@
         <v>1069</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>1069</v>
+        <v>1087</v>
       </c>
       <c r="C863" s="1">
-        <v>24.45</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="864" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13041,10 +13050,10 @@
         <v>1070</v>
       </c>
       <c r="B864" s="1" t="s">
-        <v>1070</v>
+        <v>1086</v>
       </c>
       <c r="C864" s="1">
-        <v>24.45</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="865" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14584,7 +14593,7 @@
         <v>991</v>
       </c>
       <c r="C1004" s="1">
-        <v>6</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1005" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14595,7 +14604,7 @@
         <v>992</v>
       </c>
       <c r="C1005" s="1">
-        <v>6</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1006" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14606,7 +14615,7 @@
         <v>993</v>
       </c>
       <c r="C1006" s="1">
-        <v>6</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1007" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/price-list-export.xlsx
+++ b/price-list-export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Leeukopf-Website-Official\gelitup-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFE5B35-C2BE-4464-A82C-16DBAC201BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289B573A-6D19-40E7-9860-E6E2FFDCB8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="price-list-export" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="1089">
   <si>
     <t>Item Name</t>
   </si>
@@ -3284,6 +3284,9 @@
   </si>
   <si>
     <t>Premium Builder Gel Mint 20g -HTF</t>
+  </si>
+  <si>
+    <t>Nail Clips Dual Form Single -HTF</t>
   </si>
 </sst>
 </file>
@@ -3545,7 +3548,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C1093"/>
+  <dimension ref="A1:C1094"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.33203125" customWidth="1"/>
@@ -14062,7 +14065,7 @@
         <v>943</v>
       </c>
       <c r="B956" s="1" t="s">
-        <v>943</v>
+        <v>1088</v>
       </c>
       <c r="C956" s="1">
         <v>0.75</v>
@@ -14070,32 +14073,32 @@
     </row>
     <row r="957" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B957" s="1" t="s">
-        <v>944</v>
+        <v>1088</v>
       </c>
       <c r="C957" s="1">
-        <v>0.72</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="958" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B958" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C958" s="1">
-        <v>1.0960000000000001</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="959" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B959" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C959" s="1">
         <v>1.0960000000000001</v>
@@ -14103,32 +14106,32 @@
     </row>
     <row r="960" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B960" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C960" s="1">
-        <v>0.72</v>
+        <v>1.0960000000000001</v>
       </c>
     </row>
     <row r="961" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B961" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C961" s="1">
-        <v>3.8079999999999998</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="962" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B962" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C962" s="1">
         <v>3.8079999999999998</v>
@@ -14136,10 +14139,10 @@
     </row>
     <row r="963" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B963" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C963" s="1">
         <v>3.8079999999999998</v>
@@ -14147,10 +14150,10 @@
     </row>
     <row r="964" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B964" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C964" s="1">
         <v>3.8079999999999998</v>
@@ -14158,21 +14161,21 @@
     </row>
     <row r="965" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B965" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C965" s="1">
-        <v>1.0960000000000001</v>
+        <v>3.8079999999999998</v>
       </c>
     </row>
     <row r="966" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B966" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C966" s="1">
         <v>1.0960000000000001</v>
@@ -14180,43 +14183,43 @@
     </row>
     <row r="967" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B967" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C967" s="1">
-        <v>8.6</v>
+        <v>1.0960000000000001</v>
       </c>
     </row>
     <row r="968" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B968" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C968" s="1">
-        <v>18</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="969" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B969" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C969" s="1">
-        <v>5.82</v>
+        <v>18</v>
       </c>
     </row>
     <row r="970" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B970" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C970" s="1">
         <v>5.82</v>
@@ -14224,32 +14227,32 @@
     </row>
     <row r="971" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B971" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C971" s="1">
-        <v>4.96</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="972" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B972" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C972" s="1">
-        <v>4.41</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="973" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B973" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C973" s="1">
         <v>4.41</v>
@@ -14257,32 +14260,32 @@
     </row>
     <row r="974" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B974" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C974" s="1">
-        <v>11.61</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="975" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B975" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C975" s="1">
-        <v>10.904</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="976" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B976" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C976" s="1">
         <v>10.904</v>
@@ -14290,10 +14293,10 @@
     </row>
     <row r="977" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B977" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C977" s="1">
         <v>10.904</v>
@@ -14301,21 +14304,21 @@
     </row>
     <row r="978" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B978" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C978" s="1">
-        <v>10.26</v>
+        <v>10.904</v>
       </c>
     </row>
     <row r="979" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B979" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C979" s="1">
         <v>10.26</v>
@@ -14323,21 +14326,21 @@
     </row>
     <row r="980" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B980" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C980" s="1">
-        <v>16.064</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="981" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B981" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C981" s="1">
         <v>16.064</v>
@@ -14345,10 +14348,10 @@
     </row>
     <row r="982" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B982" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C982" s="1">
         <v>16.064</v>
@@ -14356,10 +14359,10 @@
     </row>
     <row r="983" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B983" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C983" s="1">
         <v>16.064</v>
@@ -14367,21 +14370,21 @@
     </row>
     <row r="984" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B984" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C984" s="1">
-        <v>10.256</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="985" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B985" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C985" s="1">
         <v>10.256</v>
@@ -14389,10 +14392,10 @@
     </row>
     <row r="986" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B986" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C986" s="1">
         <v>10.256</v>
@@ -14400,32 +14403,32 @@
     </row>
     <row r="987" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B987" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C987" s="1">
-        <v>6.4</v>
+        <v>10.256</v>
       </c>
     </row>
     <row r="988" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B988" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C988" s="1">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="989" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B989" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C989" s="1">
         <v>5.2</v>
@@ -14433,32 +14436,32 @@
     </row>
     <row r="990" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B990" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C990" s="1">
-        <v>5.5279999999999996</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="991" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B991" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C991" s="1">
-        <v>6.38</v>
+        <v>5.5279999999999996</v>
       </c>
     </row>
     <row r="992" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B992" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C992" s="1">
         <v>6.38</v>
@@ -14466,10 +14469,10 @@
     </row>
     <row r="993" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B993" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C993" s="1">
         <v>6.38</v>
@@ -14477,10 +14480,10 @@
     </row>
     <row r="994" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B994" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C994" s="1">
         <v>6.38</v>
@@ -14488,10 +14491,10 @@
     </row>
     <row r="995" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B995" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C995" s="1">
         <v>6.38</v>
@@ -14499,10 +14502,10 @@
     </row>
     <row r="996" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B996" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C996" s="1">
         <v>6.38</v>
@@ -14510,10 +14513,10 @@
     </row>
     <row r="997" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B997" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C997" s="1">
         <v>6.38</v>
@@ -14521,21 +14524,21 @@
     </row>
     <row r="998" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B998" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C998" s="1">
-        <v>7.7279999999999998</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="999" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B999" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C999" s="1">
         <v>7.7279999999999998</v>
@@ -14543,21 +14546,21 @@
     </row>
     <row r="1000" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B1000" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C1000" s="1">
-        <v>8.968</v>
+        <v>7.7279999999999998</v>
       </c>
     </row>
     <row r="1001" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1001" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C1001" s="1">
         <v>8.968</v>
@@ -14565,10 +14568,10 @@
     </row>
     <row r="1002" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1002" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C1002" s="1">
         <v>8.968</v>
@@ -14576,10 +14579,10 @@
     </row>
     <row r="1003" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B1003" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C1003" s="1">
         <v>8.968</v>
@@ -14587,10 +14590,10 @@
     </row>
     <row r="1004" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B1004" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C1004" s="1">
         <v>8.968</v>
@@ -14598,10 +14601,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1005" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C1005" s="1">
         <v>8.968</v>
@@ -14609,10 +14612,10 @@
     </row>
     <row r="1006" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B1006" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C1006" s="1">
         <v>8.968</v>
@@ -14620,54 +14623,54 @@
     </row>
     <row r="1007" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1007" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C1007" s="1">
-        <v>15.91</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="1008" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B1008" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C1008" s="1">
-        <v>5.74</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="1009" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B1009" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C1009" s="1">
-        <v>22.576000000000001</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="1010" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B1010" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C1010" s="1">
-        <v>16.064</v>
+        <v>22.576000000000001</v>
       </c>
     </row>
     <row r="1011" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1011" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C1011" s="1">
         <v>16.064</v>
@@ -14675,10 +14678,10 @@
     </row>
     <row r="1012" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B1012" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C1012" s="1">
         <v>16.064</v>
@@ -14686,21 +14689,21 @@
     </row>
     <row r="1013" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1013" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C1013" s="1">
-        <v>12.832000000000001</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="1014" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B1014" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C1014" s="1">
         <v>12.832000000000001</v>
@@ -14708,10 +14711,10 @@
     </row>
     <row r="1015" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B1015" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C1015" s="1">
         <v>12.832000000000001</v>
@@ -14719,21 +14722,21 @@
     </row>
     <row r="1016" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B1016" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C1016" s="1">
-        <v>13.12</v>
+        <v>12.832000000000001</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B1017" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C1017" s="1">
         <v>13.12</v>
@@ -14741,10 +14744,10 @@
     </row>
     <row r="1018" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B1018" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C1018" s="1">
         <v>13.12</v>
@@ -14752,10 +14755,10 @@
     </row>
     <row r="1019" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B1019" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C1019" s="1">
         <v>13.12</v>
@@ -14763,10 +14766,10 @@
     </row>
     <row r="1020" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B1020" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C1020" s="1">
         <v>13.12</v>
@@ -14774,10 +14777,10 @@
     </row>
     <row r="1021" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B1021" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C1021" s="1">
         <v>13.12</v>
@@ -14785,54 +14788,54 @@
     </row>
     <row r="1022" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B1022" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C1022" s="1">
-        <v>13.79</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="1023" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B1023" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C1023" s="1">
-        <v>19.7</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="1024" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B1024" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C1024" s="1">
-        <v>14.128</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="1025" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B1025" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C1025" s="1">
-        <v>5.7359999999999998</v>
+        <v>14.128</v>
       </c>
     </row>
     <row r="1026" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B1026" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C1026" s="1">
         <v>5.7359999999999998</v>
@@ -14840,10 +14843,10 @@
     </row>
     <row r="1027" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B1027" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C1027" s="1">
         <v>5.7359999999999998</v>
@@ -14851,10 +14854,10 @@
     </row>
     <row r="1028" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B1028" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C1028" s="1">
         <v>5.7359999999999998</v>
@@ -14862,65 +14865,65 @@
     </row>
     <row r="1029" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B1029" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C1029" s="1">
-        <v>5.0960000000000001</v>
+        <v>5.7359999999999998</v>
       </c>
     </row>
     <row r="1030" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B1030" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C1030" s="1">
-        <v>6.3840000000000003</v>
+        <v>5.0960000000000001</v>
       </c>
     </row>
     <row r="1031" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B1031" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C1031" s="1">
-        <v>7.6719999999999997</v>
+        <v>6.3840000000000003</v>
       </c>
     </row>
     <row r="1032" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B1032" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C1032" s="1">
-        <v>8.9600000000000009</v>
+        <v>7.6719999999999997</v>
       </c>
     </row>
     <row r="1033" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B1033" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C1033" s="1">
-        <v>6.1760000000000002</v>
+        <v>8.9600000000000009</v>
       </c>
     </row>
     <row r="1034" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B1034" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C1034" s="1">
         <v>6.1760000000000002</v>
@@ -14928,10 +14931,10 @@
     </row>
     <row r="1035" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B1035" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C1035" s="1">
         <v>6.1760000000000002</v>
@@ -14939,21 +14942,21 @@
     </row>
     <row r="1036" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B1036" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C1036" s="1">
-        <v>7.992</v>
+        <v>6.1760000000000002</v>
       </c>
     </row>
     <row r="1037" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B1037" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C1037" s="1">
         <v>7.992</v>
@@ -14961,10 +14964,10 @@
     </row>
     <row r="1038" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B1038" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C1038" s="1">
         <v>7.992</v>
@@ -14972,21 +14975,21 @@
     </row>
     <row r="1039" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B1039" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C1039" s="1">
-        <v>10</v>
+        <v>7.992</v>
       </c>
     </row>
     <row r="1040" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B1040" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C1040" s="1">
         <v>10</v>
@@ -14994,10 +14997,10 @@
     </row>
     <row r="1041" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B1041" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C1041" s="1">
         <v>10</v>
@@ -15005,54 +15008,54 @@
     </row>
     <row r="1042" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B1042" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C1042" s="1">
-        <v>167.98</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1043" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B1043" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C1043" s="1">
-        <v>10.4</v>
+        <v>167.98</v>
       </c>
     </row>
     <row r="1044" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B1044" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C1044" s="1">
-        <v>58.24</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="1045" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B1045" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C1045" s="1">
-        <v>7.41</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="1046" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B1046" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C1046" s="1">
         <v>7.41</v>
@@ -15060,10 +15063,10 @@
     </row>
     <row r="1047" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B1047" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C1047" s="1">
         <v>7.41</v>
@@ -15071,10 +15074,10 @@
     </row>
     <row r="1048" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B1048" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C1048" s="1">
         <v>7.41</v>
@@ -15082,10 +15085,10 @@
     </row>
     <row r="1049" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B1049" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C1049" s="1">
         <v>7.41</v>
@@ -15093,21 +15096,21 @@
     </row>
     <row r="1050" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B1050" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C1050" s="1">
-        <v>11.3</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1051" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B1051" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C1051" s="1">
         <v>11.3</v>
@@ -15115,10 +15118,10 @@
     </row>
     <row r="1052" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1052" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B1052" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C1052" s="1">
         <v>11.3</v>
@@ -15126,10 +15129,10 @@
     </row>
     <row r="1053" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B1053" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C1053" s="1">
         <v>11.3</v>
@@ -15137,21 +15140,21 @@
     </row>
     <row r="1054" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B1054" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C1054" s="1">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="1055" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1055" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B1055" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C1055" s="1">
         <v>9.4</v>
@@ -15159,10 +15162,10 @@
     </row>
     <row r="1056" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1056" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B1056" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C1056" s="1">
         <v>9.4</v>
@@ -15170,10 +15173,10 @@
     </row>
     <row r="1057" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B1057" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C1057" s="1">
         <v>9.4</v>
@@ -15181,10 +15184,10 @@
     </row>
     <row r="1058" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1058" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B1058" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C1058" s="1">
         <v>9.4</v>
@@ -15192,10 +15195,10 @@
     </row>
     <row r="1059" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1059" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B1059" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C1059" s="1">
         <v>9.4</v>
@@ -15203,21 +15206,21 @@
     </row>
     <row r="1060" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1060" s="1" t="s">
-        <v>830</v>
+        <v>1046</v>
       </c>
       <c r="B1060" s="1" t="s">
-        <v>830</v>
+        <v>1046</v>
       </c>
       <c r="C1060" s="1">
-        <v>12.84</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="1061" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1061" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B1061" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C1061" s="1">
         <v>12.84</v>
@@ -15225,10 +15228,10 @@
     </row>
     <row r="1062" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1062" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B1062" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C1062" s="1">
         <v>12.84</v>
@@ -15236,10 +15239,10 @@
     </row>
     <row r="1063" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B1063" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C1063" s="1">
         <v>12.84</v>
@@ -15247,10 +15250,10 @@
     </row>
     <row r="1064" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B1064" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C1064" s="1">
         <v>12.84</v>
@@ -15258,32 +15261,32 @@
     </row>
     <row r="1065" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="1" t="s">
-        <v>1064</v>
+        <v>829</v>
       </c>
       <c r="B1065" s="1" t="s">
-        <v>1064</v>
+        <v>829</v>
       </c>
       <c r="C1065" s="1">
-        <v>8.25</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="1066" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="1" t="s">
-        <v>1047</v>
+        <v>1064</v>
       </c>
       <c r="B1066" s="1" t="s">
-        <v>1047</v>
+        <v>1064</v>
       </c>
       <c r="C1066" s="1">
-        <v>7.41</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="1067" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1067" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B1067" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C1067" s="1">
         <v>7.41</v>
@@ -15291,10 +15294,10 @@
     </row>
     <row r="1068" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1068" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B1068" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C1068" s="1">
         <v>7.41</v>
@@ -15302,10 +15305,10 @@
     </row>
     <row r="1069" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1069" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B1069" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C1069" s="1">
         <v>7.41</v>
@@ -15313,10 +15316,10 @@
     </row>
     <row r="1070" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1070" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B1070" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C1070" s="1">
         <v>7.41</v>
@@ -15324,10 +15327,10 @@
     </row>
     <row r="1071" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1071" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B1071" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C1071" s="1">
         <v>7.41</v>
@@ -15335,10 +15338,10 @@
     </row>
     <row r="1072" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1072" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B1072" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C1072" s="1">
         <v>7.41</v>
@@ -15346,10 +15349,10 @@
     </row>
     <row r="1073" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1073" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1073" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C1073" s="1">
         <v>7.41</v>
@@ -15357,10 +15360,10 @@
     </row>
     <row r="1074" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1074" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B1074" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C1074" s="1">
         <v>7.41</v>
@@ -15368,10 +15371,10 @@
     </row>
     <row r="1075" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1075" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B1075" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C1075" s="1">
         <v>7.41</v>
@@ -15379,10 +15382,10 @@
     </row>
     <row r="1076" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1076" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B1076" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C1076" s="1">
         <v>7.41</v>
@@ -15390,10 +15393,10 @@
     </row>
     <row r="1077" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1077" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B1077" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C1077" s="1">
         <v>7.41</v>
@@ -15401,10 +15404,10 @@
     </row>
     <row r="1078" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1078" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B1078" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C1078" s="1">
         <v>7.41</v>
@@ -15412,10 +15415,10 @@
     </row>
     <row r="1079" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1079" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B1079" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C1079" s="1">
         <v>7.41</v>
@@ -15423,10 +15426,10 @@
     </row>
     <row r="1080" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="1" t="s">
-        <v>382</v>
+        <v>1060</v>
       </c>
       <c r="B1080" s="1" t="s">
-        <v>382</v>
+        <v>1060</v>
       </c>
       <c r="C1080" s="1">
         <v>7.41</v>
@@ -15434,10 +15437,10 @@
     </row>
     <row r="1081" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B1081" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C1081" s="1">
         <v>7.41</v>
@@ -15445,10 +15448,10 @@
     </row>
     <row r="1082" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1082" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B1082" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C1082" s="1">
         <v>7.41</v>
@@ -15456,10 +15459,10 @@
     </row>
     <row r="1083" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1083" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B1083" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C1083" s="1">
         <v>7.41</v>
@@ -15467,10 +15470,10 @@
     </row>
     <row r="1084" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1084" s="1" t="s">
-        <v>1061</v>
+        <v>389</v>
       </c>
       <c r="B1084" s="1" t="s">
-        <v>1061</v>
+        <v>389</v>
       </c>
       <c r="C1084" s="1">
         <v>7.41</v>
@@ -15478,10 +15481,10 @@
     </row>
     <row r="1085" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1085" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B1085" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C1085" s="1">
         <v>7.41</v>
@@ -15489,32 +15492,32 @@
     </row>
     <row r="1086" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1086" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B1086" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C1086" s="1">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="B1086" s="1" t="s">
+      <c r="B1087" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="C1086" s="1">
-        <v>7.41</v>
-      </c>
-    </row>
-    <row r="1087" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1087" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>1078</v>
-      </c>
       <c r="C1087" s="1">
-        <v>13.65</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="1088" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B1088" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C1088" s="1">
         <v>13.65</v>
@@ -15522,10 +15525,10 @@
     </row>
     <row r="1089" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B1089" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C1089" s="1">
         <v>13.65</v>
@@ -15533,10 +15536,10 @@
     </row>
     <row r="1090" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B1090" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C1090" s="1">
         <v>13.65</v>
@@ -15544,10 +15547,10 @@
     </row>
     <row r="1091" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B1091" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C1091" s="1">
         <v>13.65</v>
@@ -15555,10 +15558,10 @@
     </row>
     <row r="1092" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B1092" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C1092" s="1">
         <v>13.65</v>
@@ -15566,12 +15569,23 @@
     </row>
     <row r="1093" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C1093" s="1">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1094" t="s">
         <v>1084</v>
       </c>
-      <c r="B1093" t="s">
+      <c r="B1094" t="s">
         <v>1084</v>
       </c>
-      <c r="C1093" s="1">
+      <c r="C1094" s="1">
         <v>13.65</v>
       </c>
     </row>
